--- a/Data/testDataNetherland.xlsx
+++ b/Data/testDataNetherland.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927F497C-9436-44F7-90B9-0A474814DD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AEFA8B9-B874-4DF3-8A45-337B3BAD08DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="114">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -216,19 +216,22 @@
     <t>ProposedPayGroupFinal</t>
   </si>
   <si>
+    <t>Failed</t>
+  </si>
+  <si>
     <t>701 Recruitment (Vulam Syhohu (8701689))</t>
   </si>
   <si>
     <t>Mevr</t>
   </si>
   <si>
-    <t>Lance</t>
+    <t>Maritza</t>
   </si>
   <si>
     <t>Test</t>
   </si>
   <si>
-    <t>Kuvalis</t>
+    <t>Kulas</t>
   </si>
   <si>
     <t>071 025 8087</t>
@@ -270,9 +273,6 @@
     <t>Undefined contract end date (Undetermined)</t>
   </si>
   <si>
-    <t>'Part-time( PT )'</t>
-  </si>
-  <si>
     <t>Active</t>
   </si>
   <si>
@@ -367,6 +367,9 @@
   </si>
   <si>
     <t>NL Management</t>
+  </si>
+  <si>
+    <t>Part-time( PT )'</t>
   </si>
 </sst>
 </file>
@@ -581,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -685,6 +688,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -989,6 +993,7 @@
     <col min="45" max="45" width="33.6328125" customWidth="1"/>
     <col min="47" max="47" width="38.453125" customWidth="1"/>
     <col min="51" max="51" width="45.7265625" customWidth="1"/>
+    <col min="64" max="64" width="40.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:64" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1187,87 +1192,89 @@
     </row>
     <row r="2" spans="1:64" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="11"/>
-      <c r="C2" s="12"/>
+      <c r="C2" s="12" t="s">
+        <v>62</v>
+      </c>
       <c r="D2" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L2" s="16">
         <f ca="1">TODAY()-31</f>
-        <v>45727</v>
+        <v>45730</v>
       </c>
       <c r="M2" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="N2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O2" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q2" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="R2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S2" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="N2" t="s">
-        <v>71</v>
-      </c>
-      <c r="O2" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q2" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="R2" t="s">
-        <v>71</v>
-      </c>
-      <c r="S2" s="15" t="s">
-        <v>69</v>
-      </c>
       <c r="T2" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U2" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V2" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="W2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y2" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z2" s="23" t="s">
         <v>80</v>
+      </c>
+      <c r="Z2" s="38" t="s">
+        <v>113</v>
       </c>
       <c r="AA2" s="24" t="s">
         <v>81</v>
       </c>
       <c r="AB2" s="20">
         <f ca="1">AG2</f>
-        <v>45727</v>
+        <v>45730</v>
       </c>
       <c r="AC2" s="25">
         <f ca="1">AG2</f>
-        <v>45727</v>
+        <v>45730</v>
       </c>
       <c r="AD2" s="26" t="s">
         <v>82</v>
@@ -1280,7 +1287,7 @@
       </c>
       <c r="AG2" s="28">
         <f ca="1">L2</f>
-        <v>45727</v>
+        <v>45730</v>
       </c>
       <c r="AH2" s="20">
         <v>44986</v>
@@ -1328,7 +1335,7 @@
         <v>94</v>
       </c>
       <c r="AW2" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AX2" s="33" t="s">
         <v>95</v>
@@ -1343,16 +1350,16 @@
         <v>97</v>
       </c>
       <c r="BB2" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="BC2" t="s">
+        <v>72</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>72</v>
+      </c>
+      <c r="BE2" s="17" t="s">
         <v>71</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>71</v>
-      </c>
-      <c r="BE2" s="17" t="s">
-        <v>70</v>
       </c>
       <c r="BF2" t="s">
         <v>98</v>
@@ -1381,64 +1388,64 @@
         <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F3" s="14"/>
       <c r="G3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H3" s="14"/>
       <c r="I3" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L3" s="16">
         <f ca="1">TODAY()-31</f>
-        <v>45727</v>
+        <v>45730</v>
       </c>
       <c r="M3" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="N3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="P3" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q3" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="R3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S3" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="N3" t="s">
-        <v>71</v>
-      </c>
-      <c r="O3" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q3" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="R3" t="s">
-        <v>71</v>
-      </c>
-      <c r="S3" s="15" t="s">
-        <v>69</v>
-      </c>
       <c r="T3" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V3" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="W3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y3" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z3" s="22" t="s">
         <v>106</v>
@@ -1448,11 +1455,11 @@
       </c>
       <c r="AB3" s="20">
         <f ca="1">AG3</f>
-        <v>45727</v>
+        <v>45730</v>
       </c>
       <c r="AC3" s="25">
         <f ca="1">AG3</f>
-        <v>45727</v>
+        <v>45730</v>
       </c>
       <c r="AD3" s="26" t="s">
         <v>82</v>
@@ -1461,7 +1468,7 @@
       <c r="AF3" s="23"/>
       <c r="AG3" s="28">
         <f ca="1">L3</f>
-        <v>45727</v>
+        <v>45730</v>
       </c>
       <c r="AH3" s="20"/>
       <c r="AI3" s="15" t="s">
@@ -1507,7 +1514,7 @@
         <v>251</v>
       </c>
       <c r="AW3" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AX3" s="33" t="s">
         <v>95</v>
@@ -1522,16 +1529,16 @@
         <v>35591</v>
       </c>
       <c r="BB3" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="BC3" t="s">
+        <v>72</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>72</v>
+      </c>
+      <c r="BE3" s="17" t="s">
         <v>71</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>71</v>
-      </c>
-      <c r="BE3" s="17" t="s">
-        <v>70</v>
       </c>
       <c r="BF3" t="s">
         <v>98</v>
